--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N179_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N179_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>54.70895179009619</v>
+        <v>8.89020466589063</v>
       </c>
       <c r="D2" t="n">
-        <v>55.29689367318104</v>
+        <v>8.98574522189192</v>
       </c>
       <c r="E2" t="n">
-        <v>14.12621983087596</v>
+        <v>2.295510722517344</v>
       </c>
       <c r="F2" t="n">
-        <v>14.81441358094718</v>
+        <v>2.407342206903917</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.1806911546233</v>
+        <v>4.416862312626286</v>
       </c>
       <c r="D3" t="n">
-        <v>25.01910191049381</v>
+        <v>4.065604060455244</v>
       </c>
       <c r="E3" t="n">
-        <v>14.12621983087596</v>
+        <v>2.295510722517344</v>
       </c>
       <c r="F3" t="n">
-        <v>14.81441358094718</v>
+        <v>2.407342206903917</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.00015609163629</v>
+        <v>5.687525364890898</v>
       </c>
       <c r="D4" t="n">
-        <v>35.5682842435936</v>
+        <v>5.779846189583961</v>
       </c>
       <c r="E4" t="n">
-        <v>14.12621983087596</v>
+        <v>2.295510722517344</v>
       </c>
       <c r="F4" t="n">
-        <v>14.81441358094718</v>
+        <v>2.407342206903917</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.97914777966647</v>
+        <v>3.734111514195802</v>
       </c>
       <c r="D5" t="n">
-        <v>19.83213807892758</v>
+        <v>3.222722437825731</v>
       </c>
       <c r="E5" t="n">
-        <v>14.12621983087596</v>
+        <v>2.295510722517344</v>
       </c>
       <c r="F5" t="n">
-        <v>14.81441358094718</v>
+        <v>2.407342206903917</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.38218640737018</v>
+        <v>7.212105291197656</v>
       </c>
       <c r="D6" t="n">
-        <v>44.65367093879066</v>
+        <v>7.256221527553483</v>
       </c>
       <c r="E6" t="n">
-        <v>14.12621983087596</v>
+        <v>2.295510722517344</v>
       </c>
       <c r="F6" t="n">
-        <v>14.81441358094718</v>
+        <v>2.407342206903917</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.69023501130206</v>
+        <v>4.174663189336585</v>
       </c>
       <c r="D7" t="n">
-        <v>20.47983425497167</v>
+        <v>3.327973066432897</v>
       </c>
       <c r="E7" t="n">
-        <v>14.12621983087596</v>
+        <v>2.295510722517344</v>
       </c>
       <c r="F7" t="n">
-        <v>14.81441358094718</v>
+        <v>2.407342206903917</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.38132795490506</v>
+        <v>5.261965792672073</v>
       </c>
       <c r="D8" t="n">
-        <v>32.08950750372791</v>
+        <v>5.214544969355785</v>
       </c>
       <c r="E8" t="n">
-        <v>14.12621983087596</v>
+        <v>2.295510722517344</v>
       </c>
       <c r="F8" t="n">
-        <v>14.81441358094718</v>
+        <v>2.407342206903917</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.91100021706917</v>
+        <v>4.53553753527374</v>
       </c>
       <c r="D9" t="n">
-        <v>28.18689316955755</v>
+        <v>4.580370140053102</v>
       </c>
       <c r="E9" t="n">
-        <v>14.12621983087596</v>
+        <v>2.295510722517344</v>
       </c>
       <c r="F9" t="n">
-        <v>14.81441358094718</v>
+        <v>2.407342206903917</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>67.33821345827918</v>
+        <v>10.94245968697037</v>
       </c>
       <c r="D10" t="n">
-        <v>67.30234349745311</v>
+        <v>10.93663081833613</v>
       </c>
       <c r="E10" t="n">
-        <v>14.12621983087596</v>
+        <v>2.295510722517344</v>
       </c>
       <c r="F10" t="n">
-        <v>14.81441358094718</v>
+        <v>2.407342206903917</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>45.632114885105</v>
+        <v>7.415218668829564</v>
       </c>
       <c r="D11" t="n">
-        <v>44.12043467294148</v>
+        <v>7.169570634352991</v>
       </c>
       <c r="E11" t="n">
-        <v>14.12621983087596</v>
+        <v>2.295510722517344</v>
       </c>
       <c r="F11" t="n">
-        <v>14.81441358094718</v>
+        <v>2.407342206903917</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>44.11682365176104</v>
+        <v>7.168983843411169</v>
       </c>
       <c r="D12" t="n">
-        <v>42.43229901855425</v>
+        <v>6.895248590515067</v>
       </c>
       <c r="E12" t="n">
-        <v>14.12621983087596</v>
+        <v>2.295510722517344</v>
       </c>
       <c r="F12" t="n">
-        <v>14.81441358094718</v>
+        <v>2.407342206903917</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>29.12323224751355</v>
+        <v>4.732525240220951</v>
       </c>
       <c r="D13" t="n">
-        <v>29.04806047146787</v>
+        <v>4.720309826613528</v>
       </c>
       <c r="E13" t="n">
-        <v>14.12621983087596</v>
+        <v>2.295510722517344</v>
       </c>
       <c r="F13" t="n">
-        <v>14.81441358094718</v>
+        <v>2.407342206903917</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>56.48835291914664</v>
+        <v>9.179357349361331</v>
       </c>
       <c r="D14" t="n">
-        <v>56.63880302210261</v>
+        <v>9.203805491091673</v>
       </c>
       <c r="E14" t="n">
-        <v>14.12621983087596</v>
+        <v>2.295510722517344</v>
       </c>
       <c r="F14" t="n">
-        <v>14.81441358094718</v>
+        <v>2.407342206903917</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>18.96247706547464</v>
+        <v>3.08140252313963</v>
       </c>
       <c r="D15" t="n">
-        <v>18.68530575173962</v>
+        <v>3.036362184657688</v>
       </c>
       <c r="E15" t="n">
-        <v>14.12621983087596</v>
+        <v>2.295510722517344</v>
       </c>
       <c r="F15" t="n">
-        <v>14.81441358094718</v>
+        <v>2.407342206903917</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>37.14490315746069</v>
+        <v>6.036046763087362</v>
       </c>
       <c r="D16" t="n">
-        <v>36.83754782060724</v>
+        <v>5.986101520848677</v>
       </c>
       <c r="E16" t="n">
-        <v>14.12621983087596</v>
+        <v>2.295510722517344</v>
       </c>
       <c r="F16" t="n">
-        <v>14.81441358094718</v>
+        <v>2.407342206903917</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>60.94209959215124</v>
+        <v>9.903091183724577</v>
       </c>
       <c r="D17" t="n">
-        <v>60.63913576443936</v>
+        <v>9.853859561721396</v>
       </c>
       <c r="E17" t="n">
-        <v>14.12621983087596</v>
+        <v>2.295510722517344</v>
       </c>
       <c r="F17" t="n">
-        <v>14.81441358094718</v>
+        <v>2.407342206903917</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
